--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_nuble.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_nuble.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>28.57029608783543</v>
+      </c>
+      <c r="C2">
         <v>27.11562091244203</v>
-      </c>
-      <c r="C2">
-        <v>28.57029608783543</v>
       </c>
       <c r="D2">
         <v>3.687911124104663</v>
       </c>
       <c r="E2">
-        <v>17.4168745862824</v>
+        <v>18.35123987983095</v>
       </c>
       <c r="F2">
         <v>64.23188553388665</v>
       </c>
       <c r="G2">
-        <v>18.35123987983095</v>
+        <v>17.41687458628239</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.73034905409006</v>
+      </c>
+      <c r="C3">
         <v>30.80202504662936</v>
-      </c>
-      <c r="C3">
-        <v>28.73034905409006</v>
       </c>
       <c r="D3">
         <v>3.246539792387543</v>
       </c>
       <c r="E3">
-        <v>19.30769551964591</v>
+        <v>18.00910267652094</v>
       </c>
       <c r="F3">
         <v>62.68320180383315</v>
       </c>
       <c r="G3">
-        <v>18.00910267652094</v>
+        <v>19.30769551964591</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>30.96087057189164</v>
+      </c>
+      <c r="C4">
         <v>21.43551748089835</v>
-      </c>
-      <c r="C4">
-        <v>30.96087057189164</v>
       </c>
       <c r="D4">
         <v>4.665154461006697</v>
       </c>
       <c r="E4">
+        <v>20.31601336979642</v>
+      </c>
+      <c r="F4">
+        <v>65.61835308416896</v>
+      </c>
+      <c r="G4">
         <v>14.06563354603464</v>
-      </c>
-      <c r="F4">
-        <v>65.61835308416894</v>
-      </c>
-      <c r="G4">
-        <v>20.31601336979642</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>28.73327708810414</v>
+      </c>
+      <c r="C5">
         <v>32.92756417982403</v>
-      </c>
-      <c r="C5">
-        <v>28.73327708810414</v>
       </c>
       <c r="D5">
         <v>3.03696925329429</v>
       </c>
       <c r="E5">
-        <v>20.36829941101916</v>
+        <v>17.77380153582346</v>
       </c>
       <c r="F5">
         <v>61.85789905315739</v>
       </c>
       <c r="G5">
-        <v>17.77380153582346</v>
+        <v>20.36829941101916</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>28.9588801399825</v>
+      </c>
+      <c r="C6">
         <v>31.35608048993876</v>
-      </c>
-      <c r="C6">
-        <v>28.9588801399825</v>
       </c>
       <c r="D6">
         <v>3.189174107142857</v>
       </c>
       <c r="E6">
-        <v>19.55904824274176</v>
+        <v>18.06374154114822</v>
       </c>
       <c r="F6">
         <v>62.37721021611002</v>
       </c>
       <c r="G6">
-        <v>18.06374154114822</v>
+        <v>19.55904824274176</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>27.00051626226123</v>
+      </c>
+      <c r="C7">
         <v>32.58905524006195</v>
-      </c>
-      <c r="C7">
-        <v>27.00051626226123</v>
       </c>
       <c r="D7">
         <v>3.068514851485149</v>
       </c>
       <c r="E7">
-        <v>20.42054185200162</v>
+        <v>16.91872219975738</v>
       </c>
       <c r="F7">
         <v>62.660735948241</v>
       </c>
       <c r="G7">
-        <v>16.91872219975738</v>
+        <v>20.42054185200162</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>27.92287467134093</v>
+      </c>
+      <c r="C8">
         <v>38.66783523225241</v>
-      </c>
-      <c r="C8">
-        <v>27.92287467134093</v>
       </c>
       <c r="D8">
         <v>2.586128739800544</v>
       </c>
       <c r="E8">
-        <v>23.21127946127946</v>
+        <v>16.76136363636364</v>
       </c>
       <c r="F8">
         <v>60.02735690235691</v>
       </c>
       <c r="G8">
-        <v>16.76136363636364</v>
+        <v>23.21127946127946</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>28.47782736682176</v>
+      </c>
+      <c r="C9">
         <v>34.32722438514861</v>
-      </c>
-      <c r="C9">
-        <v>28.47782736682176</v>
       </c>
       <c r="D9">
         <v>2.91313969571231</v>
       </c>
       <c r="E9">
-        <v>21.084864391951</v>
+        <v>17.49198016914552</v>
       </c>
       <c r="F9">
         <v>61.42315543890346</v>
       </c>
       <c r="G9">
-        <v>17.49198016914552</v>
+        <v>21.084864391951</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>29.39186331726296</v>
+      </c>
+      <c r="C10">
         <v>31.71783811215427</v>
-      </c>
-      <c r="C10">
-        <v>29.39186331726296</v>
       </c>
       <c r="D10">
         <v>3.1528</v>
       </c>
       <c r="E10">
-        <v>19.68710625787484</v>
+        <v>18.24338513229736</v>
       </c>
       <c r="F10">
         <v>62.0695086098278</v>
       </c>
       <c r="G10">
-        <v>18.24338513229736</v>
+        <v>19.68710625787484</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>27.52729608220938</v>
+      </c>
+      <c r="C11">
         <v>34.50224791265254</v>
-      </c>
-      <c r="C11">
-        <v>27.52729608220938</v>
       </c>
       <c r="D11">
         <v>2.898361876396128</v>
       </c>
       <c r="E11">
-        <v>21.29380053908356</v>
+        <v>16.98905977485334</v>
       </c>
       <c r="F11">
         <v>61.71713968606311</v>
       </c>
       <c r="G11">
-        <v>16.98905977485334</v>
+        <v>21.29380053908356</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>25.1434034416826</v>
+      </c>
+      <c r="C12">
         <v>44.295729764181</v>
-      </c>
-      <c r="C12">
-        <v>25.1434034416826</v>
       </c>
       <c r="D12">
         <v>2.257553956834532</v>
       </c>
       <c r="E12">
-        <v>26.14256159488433</v>
+        <v>14.83919503479406</v>
       </c>
       <c r="F12">
         <v>59.01824337032161</v>
       </c>
       <c r="G12">
-        <v>14.83919503479406</v>
+        <v>26.14256159488433</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>28.4377838328792</v>
+      </c>
+      <c r="C13">
         <v>33.50590372388738</v>
-      </c>
-      <c r="C13">
-        <v>28.4377838328792</v>
       </c>
       <c r="D13">
         <v>2.984548658172947</v>
       </c>
       <c r="E13">
-        <v>20.68984856982614</v>
+        <v>17.56029164329781</v>
       </c>
       <c r="F13">
         <v>61.74985978687605</v>
       </c>
       <c r="G13">
-        <v>17.56029164329781</v>
+        <v>20.68984856982614</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>25.17985611510791</v>
+      </c>
+      <c r="C14">
         <v>41.12230215827338</v>
-      </c>
-      <c r="C14">
-        <v>25.17985611510791</v>
       </c>
       <c r="D14">
         <v>2.431770468859342</v>
       </c>
       <c r="E14">
+        <v>15.14102785949126</v>
+      </c>
+      <c r="F14">
+        <v>60.13151064197959</v>
+      </c>
+      <c r="G14">
         <v>24.72746149852916</v>
-      </c>
-      <c r="F14">
-        <v>60.13151064197957</v>
-      </c>
-      <c r="G14">
-        <v>15.14102785949126</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>27.39553879987433</v>
+      </c>
+      <c r="C15">
         <v>39.67954759660697</v>
-      </c>
-      <c r="C15">
-        <v>27.39553879987433</v>
       </c>
       <c r="D15">
         <v>2.520190023752969</v>
       </c>
       <c r="E15">
-        <v>23.74952989845806</v>
+        <v>16.39714178262505</v>
       </c>
       <c r="F15">
         <v>59.85332831891689</v>
       </c>
       <c r="G15">
-        <v>16.39714178262505</v>
+        <v>23.74952989845806</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>28.92265193370166</v>
+      </c>
+      <c r="C16">
         <v>45</v>
-      </c>
-      <c r="C16">
-        <v>28.92265193370166</v>
       </c>
       <c r="D16">
         <v>2.222222222222222</v>
       </c>
       <c r="E16">
-        <v>25.87357052096569</v>
+        <v>16.62960609911055</v>
       </c>
       <c r="F16">
         <v>57.49682337992375</v>
       </c>
       <c r="G16">
-        <v>16.62960609911055</v>
+        <v>25.87357052096569</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>24.65968586387434</v>
+      </c>
+      <c r="C17">
         <v>36.2565445026178</v>
-      </c>
-      <c r="C17">
-        <v>24.65968586387434</v>
       </c>
       <c r="D17">
         <v>2.758122743682311</v>
       </c>
       <c r="E17">
-        <v>22.53131608914918</v>
+        <v>15.3245485602733</v>
       </c>
       <c r="F17">
         <v>62.14413535057752</v>
       </c>
       <c r="G17">
-        <v>15.3245485602733</v>
+        <v>22.53131608914918</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>28.25536598789213</v>
+      </c>
+      <c r="C18">
         <v>30.87782058337919</v>
-      </c>
-      <c r="C18">
-        <v>28.25536598789213</v>
       </c>
       <c r="D18">
         <v>3.23857053738526</v>
       </c>
       <c r="E18">
-        <v>19.40375935949091</v>
+        <v>17.75579726434834</v>
       </c>
       <c r="F18">
         <v>62.84044337616075</v>
       </c>
       <c r="G18">
-        <v>17.75579726434834</v>
+        <v>19.40375935949091</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>31.21316579561881</v>
+      </c>
+      <c r="C19">
         <v>25.62548648949183</v>
-      </c>
-      <c r="C19">
-        <v>31.21316579561881</v>
       </c>
       <c r="D19">
         <v>3.902364938164461</v>
       </c>
       <c r="E19">
-        <v>16.33875713424793</v>
+        <v>19.90144989187848</v>
       </c>
       <c r="F19">
         <v>63.75979297387359</v>
       </c>
       <c r="G19">
-        <v>19.90144989187848</v>
+        <v>16.33875713424793</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>24.02388059701493</v>
+      </c>
+      <c r="C20">
         <v>38.2089552238806</v>
-      </c>
-      <c r="C20">
-        <v>24.02388059701493</v>
       </c>
       <c r="D20">
         <v>2.6171875</v>
       </c>
       <c r="E20">
-        <v>23.55192463384117</v>
+        <v>14.80827261352764</v>
       </c>
       <c r="F20">
         <v>61.63980275263119</v>
       </c>
       <c r="G20">
-        <v>14.80827261352764</v>
+        <v>23.55192463384117</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>30.92892329345531</v>
+      </c>
+      <c r="C21">
         <v>38.74032371569317</v>
-      </c>
-      <c r="C21">
-        <v>30.92892329345531</v>
       </c>
       <c r="D21">
         <v>2.581289736603088</v>
       </c>
       <c r="E21">
-        <v>22.83284944006636</v>
+        <v>18.22895064288677</v>
       </c>
       <c r="F21">
         <v>58.93819991704687</v>
       </c>
       <c r="G21">
-        <v>18.22895064288677</v>
+        <v>22.83284944006636</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>27.3758536867693</v>
+      </c>
+      <c r="C22">
         <v>31.02210904039819</v>
-      </c>
-      <c r="C22">
-        <v>27.3758536867693</v>
       </c>
       <c r="D22">
         <v>3.223507462686567</v>
       </c>
       <c r="E22">
-        <v>19.58491669102601</v>
+        <v>17.28295819935692</v>
       </c>
       <c r="F22">
         <v>63.13212510961706</v>
       </c>
       <c r="G22">
-        <v>17.28295819935692</v>
+        <v>19.58491669102601</v>
       </c>
     </row>
   </sheetData>
